--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rcaf977961eee47b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rbc8f06632d774e32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R2d966f29400e4c03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R614f22d5f4b34a6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rfd2946d310e44a5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R9bf652594f264803"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Ra5a1afd5535243da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rbd505765317c4479"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Re43c87a051bb4959"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R28572ccd601a4c81"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -812,7 +812,7 @@
         <x:v>output/configs/alpha/checkout_v2.json；output/configs/alpha/notify_center.json；output/configs/gamma/notify_center.json；output/configs/gamma/search_boost.json</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
-        <x:v>租户矩阵与reference.zip成员</x:v>
+        <x:v>租户矩阵与正式交付目录中的配置文件</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="50" customHeight="1">
